--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003550</t>
-  </si>
-  <si>
-    <t>CIPTADENT FRS.MIN190</t>
+    <t>10008989</t>
+  </si>
+  <si>
+    <t>BIMOLI MYK.GRG REF2L</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -31,64 +31,16 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139068</t>
-  </si>
-  <si>
-    <t>CPTDENT FRESH MC 190</t>
-  </si>
-  <si>
-    <t>10004051</t>
-  </si>
-  <si>
-    <t>CIPTADENT COOL MN190</t>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20093188</t>
-  </si>
-  <si>
-    <t>RNSO MLT G.LQ 510 G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO LIQ PRFM 510 G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20122879</t>
-  </si>
-  <si>
-    <t>RNSO MLT K STR 510 G</t>
-  </si>
-  <si>
-    <t>20140001</t>
-  </si>
-  <si>
-    <t>RNSO PURE LIQ 510 G</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RNSO ROSE FRS 510 G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -481,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -544,130 +496,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG SPC 80 G</t>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GR 2 L</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,76 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMI GR C.IJO 85 G</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KRI AYAM 72 G</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MYK BTL 2 L</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMI GR RNDNG 91 G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACH 90 G</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMI GR AY.GP 85 G</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE A/BW 70 G</t>
+    <t>10038967</t>
+  </si>
+  <si>
+    <t>NICE FC TISU LVG1000</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR/A 72 G</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR/S 75 G</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SEDAAP MI S/LKS 83 G</t>
-  </si>
-  <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM 77 G</t>
+    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -490,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -553,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -561,10 +513,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -573,170 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GR 2 L</t>
+    <t>10008989</t>
+  </si>
+  <si>
+    <t>BIMOLI MYK REF 2 L</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,28 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20037566</t>
+  </si>
+  <si>
+    <t>SOVIA MYK GR PCH 2 L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MYK BTL 2 L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10038967</t>
-  </si>
-  <si>
-    <t>NICE FC TISU LVG1000</t>
+    <t>20140913</t>
+  </si>
+  <si>
+    <t>SOVIA MYK GR 1.8 L</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT</t>
   </si>
 </sst>
 </file>
@@ -508,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
